--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ALABAMA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ALABAMA_2011.xlsx
@@ -1003,7 +1003,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="37">
@@ -1255,7 +1255,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="51">
@@ -1705,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="76">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C140">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C158">
@@ -4279,7 +4279,7 @@
         <v>7</v>
       </c>
       <c r="D218">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="219">
@@ -4441,7 +4441,7 @@
         <v>7</v>
       </c>
       <c r="D227">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="228">
@@ -4639,7 +4639,7 @@
         <v>7</v>
       </c>
       <c r="D238">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="239">
@@ -6835,7 +6835,7 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="361">
@@ -8689,7 +8689,7 @@
         <v>7</v>
       </c>
       <c r="D463">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="464">
@@ -9679,7 +9679,7 @@
         <v>7</v>
       </c>
       <c r="D518">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="519">
@@ -10093,7 +10093,7 @@
         <v>7</v>
       </c>
       <c r="D541">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="542">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C548">
@@ -10939,7 +10939,7 @@
         <v>7</v>
       </c>
       <c r="D588">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="589">
@@ -11047,7 +11047,7 @@
         <v>7</v>
       </c>
       <c r="D594">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="595">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C610">
@@ -12037,7 +12037,7 @@
         <v>7</v>
       </c>
       <c r="D649">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="650">
@@ -12073,7 +12073,7 @@
         <v>7</v>
       </c>
       <c r="D651">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="652">
@@ -14089,7 +14089,7 @@
         <v>7</v>
       </c>
       <c r="D763">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="764">
@@ -15655,7 +15655,7 @@
         <v>7</v>
       </c>
       <c r="D850">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="851">
@@ -15727,7 +15727,7 @@
         <v>7</v>
       </c>
       <c r="D854">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="855">
@@ -16231,7 +16231,7 @@
         <v>7</v>
       </c>
       <c r="D882">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="883">
@@ -16339,7 +16339,7 @@
         <v>7</v>
       </c>
       <c r="D888">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="889">
@@ -17203,7 +17203,7 @@
         <v>7</v>
       </c>
       <c r="D936">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="937">
@@ -17275,7 +17275,7 @@
         <v>7</v>
       </c>
       <c r="D940">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="941">
@@ -17851,7 +17851,7 @@
         <v>7</v>
       </c>
       <c r="D972">
-        <v>0.000957461359595</v>
+        <v>0.0009574613595950002</v>
       </c>
     </row>
     <row r="973">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1000">
